--- a/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
+++ b/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\coding\AIMSS\StateOfPractice\DomainMeasurements\InverseKinematics-Ryan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625BD0F3-BA1C-42A9-AF93-5D40CA423364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB7685C-2DA2-44BE-B8EB-E9F8377B22D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="appendix-B-wide-summary" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="404">
   <si>
     <t>Metric
 指标（见附录 A 与附录 B）</t>
@@ -187,12 +187,6 @@
     <t>https://developer.nvidia.com/physx-sdk</t>
   </si>
   <si>
-    <t>https://drake.mit.edu</t>
-  </si>
-  <si>
-    <t>https://dartsim.github.io</t>
-  </si>
-  <si>
     <t>https://carla.org</t>
   </si>
   <si>
@@ -623,12 +617,6 @@
     <t>https://github.com/microsoft/AirSim</t>
   </si>
   <si>
-    <t>https://github.com/RobotLocomotion/drake</t>
-  </si>
-  <si>
-    <t>https://github.com/dartsim/dart</t>
-  </si>
-  <si>
     <t>https://github.com/carla-simulator/carla</t>
   </si>
   <si>
@@ -703,9 +691,6 @@
   </si>
   <si>
     <t>C++, Python, other (Unreal Engine Blueprint scripting)</t>
-  </si>
-  <si>
-    <t>C++, Python (dartpy bindings)</t>
   </si>
   <si>
     <t>Python, other (Blender Python API; C for performance-critical components)</t>
@@ -1327,6 +1312,43 @@
   </si>
   <si>
     <t xml:space="preserve">C++, Python, other </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://drake.mit.edu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/RobotLocomotion/drake</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3, Linux</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The installation and testing  do not match. After installing with pip, running the program results in a “file not found” error.cd src
+python3 particle_test.py</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dartsim.github.io</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>funded</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ubuntu, Archlinux, FreeBSD, macOS, and Windows.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/dartsim/dart</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">C++, Python </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1444,7 +1466,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1522,6 +1544,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1865,10 +1890,10 @@
   <cols>
     <col min="1" max="1" width="65" style="25" customWidth="1"/>
     <col min="2" max="9" width="62.5" style="15" customWidth="1"/>
-    <col min="10" max="10" width="62.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="62.5" customWidth="1"/>
-    <col min="12" max="12" width="62.5" style="1" customWidth="1"/>
-    <col min="13" max="30" width="62.5" style="15" customWidth="1"/>
+    <col min="10" max="11" width="62.5" style="4" customWidth="1"/>
+    <col min="12" max="12" width="62.5" customWidth="1"/>
+    <col min="13" max="13" width="62.5" style="1" customWidth="1"/>
+    <col min="14" max="30" width="62.5" style="15" customWidth="1"/>
     <col min="31" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
@@ -1903,13 +1928,13 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="K1" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="L1" t="s">
+        <v>392</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
@@ -1993,13 +2018,13 @@
       <c r="J2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -2083,248 +2108,248 @@
       <c r="J3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K3" t="s">
-        <v>392</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="K3" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="L3" t="s">
+        <v>395</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="AD3" s="3"/>
     </row>
     <row r="4" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="L4" t="s">
         <v>81</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="AB4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="AD4" s="3"/>
     </row>
     <row r="5" spans="1:30" ht="53.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="L5" t="s">
         <v>110</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="U5" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="X5" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="Y5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="Z5" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="AA5" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="Z5" s="3" t="s">
+      <c r="AB5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AC5" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AC5" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="AD5" s="3"/>
     </row>
     <row r="6" spans="1:30" s="11" customFormat="1" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -2335,9 +2360,9 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
-      <c r="K6"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="9"/>
+      <c r="K6" s="4"/>
+      <c r="L6"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="9"/>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
@@ -2358,187 +2383,187 @@
     </row>
     <row r="7" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="H7" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="K7" t="s">
-        <v>135</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="L7" t="s">
+        <v>132</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC7" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AD7" s="3"/>
     </row>
     <row r="8" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="E8" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="F8" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="O8" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="P8" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" t="s">
-        <v>144</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="O8" s="13" t="s">
+      <c r="Q8" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="P8" s="13" t="s">
+      <c r="R8" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="S8" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="R8" s="13" t="s">
+      <c r="T8" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="S8" s="13" t="s">
+      <c r="U8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="W8" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="T8" s="13" t="s">
+      <c r="X8" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y8" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="U8" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="W8" s="13" t="s">
+      <c r="Z8" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="X8" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y8" s="13" t="s">
+      <c r="AA8" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Z8" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA8" s="13" t="s">
-        <v>155</v>
-      </c>
       <c r="AB8" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AC8" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AD8" s="12"/>
     </row>
     <row r="9" spans="1:30" s="11" customFormat="1" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -2549,9 +2574,9 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-      <c r="K9"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="9"/>
+      <c r="K9" s="4"/>
+      <c r="L9"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
@@ -2572,457 +2597,457 @@
     </row>
     <row r="10" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="H10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K10" t="s">
-        <v>158</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="L10" t="s">
+        <v>393</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AC10" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AD10" s="4"/>
     </row>
     <row r="11" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="H11" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="L11" t="s">
+        <v>164</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K11" t="s">
+      <c r="T11" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="S11" s="3" t="s">
+      <c r="U11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="V11" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="W11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AC11" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="W11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="AD11" s="3"/>
     </row>
     <row r="12" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="J12" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="L12" t="s">
+        <v>174</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="O12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="V12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="W12" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="X12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y12" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="Z12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA12" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="AB12" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AD12" s="3"/>
     </row>
     <row r="13" spans="1:30" ht="84.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K13" t="s">
-        <v>180</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="L13" t="s">
+        <v>178</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AD13" s="3"/>
     </row>
     <row r="14" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="K14" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Y14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AD14" s="3"/>
     </row>
     <row r="15" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -3051,13 +3076,13 @@
       <c r="J15" s="4">
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="4">
         <v>1</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15">
         <v>1</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="1">
         <v>1</v>
       </c>
       <c r="N15" s="3">
@@ -3112,282 +3137,281 @@
     </row>
     <row r="16" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="L16" t="s">
+        <v>396</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="N16" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="K16" t="s">
+      <c r="O16" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="P16" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="R16" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="S16" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="T16" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="Y16" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="Z16" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="AA16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB16" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="AC16" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="Y16" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z16" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB16" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC16" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="AD16" s="4"/>
     </row>
     <row r="17" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="J17" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="L17" t="s">
+        <v>394</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="O17" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="P17" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="Q17" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="K17" t="s">
-        <v>393</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="R17" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="S17" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="O17" s="4" t="s">
+      <c r="T17" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="U17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="Q17" s="4" t="s">
+      <c r="W17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="X17" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="Y17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z17" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="AA17" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="T17" s="4" t="s">
+      <c r="AB17" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="U17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="V17" s="4" t="s">
+      <c r="AC17" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="W17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="X17" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y17" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z17" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="AA17" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="AB17" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="AC17" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="AD17" s="4"/>
     </row>
     <row r="18" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K18" t="s">
-        <v>237</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L18" t="s">
+        <v>232</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="3"/>
     </row>
     <row r="19" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -3411,7 +3435,6 @@
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -3435,7 +3458,6 @@
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-      <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -3465,9 +3487,9 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-      <c r="K22"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="17"/>
+      <c r="K22" s="4"/>
+      <c r="L22"/>
+      <c r="M22" s="1"/>
       <c r="N22" s="17"/>
       <c r="O22" s="17"/>
       <c r="P22" s="17"/>
@@ -3488,907 +3510,907 @@
     </row>
     <row r="23" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K23" t="s">
-        <v>237</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>237</v>
+        <v>379</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L23" t="s">
+        <v>232</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC23" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD23" s="3"/>
     </row>
     <row r="24" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="K24" t="s">
-        <v>237</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>237</v>
+        <v>381</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L24" t="s">
+        <v>232</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC24" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD24" s="3"/>
     </row>
     <row r="25" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="K25" t="s">
-        <v>237</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>237</v>
+        <v>381</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L25" t="s">
+        <v>232</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC25" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD25" s="3"/>
     </row>
     <row r="26" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K26" t="s">
-        <v>237</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L26" t="s">
+        <v>232</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC26" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD26" s="3"/>
     </row>
     <row r="27" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="K27" t="s">
-        <v>237</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>237</v>
+        <v>380</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L27" t="s">
+        <v>232</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC27" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD27" s="3"/>
     </row>
     <row r="28" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K28" t="s">
-        <v>237</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>237</v>
+        <v>379</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L28" t="s">
+        <v>232</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC28" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD28" s="3"/>
     </row>
     <row r="29" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K29" t="s">
-        <v>237</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L29" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y29" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AC29" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD29" s="3"/>
     </row>
     <row r="30" spans="1:30" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K30" t="s">
-        <v>237</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>237</v>
+        <v>379</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L30" t="s">
+        <v>232</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD30" s="3"/>
     </row>
     <row r="31" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E31" s="4">
         <v>3</v>
       </c>
       <c r="F31" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="L31" t="s">
+        <v>397</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="P31" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="Q31" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="R31" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="S31" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="T31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="W31" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="K31" t="s">
-        <v>395</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q31" s="3" t="s">
+      <c r="X31" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA31" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB31" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="R31" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="V31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="W31" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="X31" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y31" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z31" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB31" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="AC31" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AD31" s="3"/>
     </row>
     <row r="32" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="K32" t="s">
-        <v>177</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>177</v>
+        <v>383</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="L32" t="s">
+        <v>175</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Y32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Z32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AB32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC32" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AD32" s="3"/>
     </row>
     <row r="33" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B33" s="3">
         <v>3</v>
@@ -4417,13 +4439,13 @@
       <c r="J33" s="4">
         <v>0</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="4">
         <v>0</v>
       </c>
-      <c r="L33" s="1">
-        <v>1</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <v>2</v>
       </c>
       <c r="N33" s="3">
@@ -4478,277 +4500,277 @@
     </row>
     <row r="34" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K34" t="s">
-        <v>237</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>237</v>
+        <v>379</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L34" t="s">
+        <v>232</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC34" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD34" s="3"/>
     </row>
     <row r="35" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K35" t="s">
-        <v>237</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>237</v>
+        <v>379</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L35" t="s">
+        <v>232</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC35" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD35" s="3"/>
     </row>
     <row r="36" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K36" t="s">
-        <v>240</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L36" t="s">
+        <v>235</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Y36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AC36" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AD36" s="3"/>
     </row>
     <row r="37" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B37" s="3">
         <v>10</v>
@@ -4777,13 +4799,13 @@
       <c r="J37" s="4">
         <v>4</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="4">
         <v>8</v>
       </c>
-      <c r="L37" s="1">
-        <v>9</v>
-      </c>
-      <c r="M37" s="3">
+      <c r="L37">
+        <v>7</v>
+      </c>
+      <c r="M37" s="1">
         <v>8</v>
       </c>
       <c r="N37" s="3">
@@ -4838,15 +4860,17 @@
     </row>
     <row r="38" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="M38" s="3"/>
+        <v>259</v>
+      </c>
+      <c r="L38" t="s">
+        <v>398</v>
+      </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
@@ -4870,7 +4894,6 @@
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
-      <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
@@ -4894,7 +4917,6 @@
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
-      <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
@@ -4924,9 +4946,9 @@
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-      <c r="K41"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="17"/>
+      <c r="K41" s="4"/>
+      <c r="L41"/>
+      <c r="M41" s="1"/>
       <c r="N41" s="17"/>
       <c r="O41" s="17"/>
       <c r="P41" s="17"/>
@@ -4947,725 +4969,725 @@
     </row>
     <row r="42" spans="1:30" ht="55.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K42" t="s">
-        <v>237</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L42" t="s">
+        <v>232</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC42" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD42" s="3"/>
     </row>
     <row r="43" spans="1:30" s="11" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="I43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="L43" t="s">
         <v>267</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="M43" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N43" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="O43" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="P43" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q43" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="H43" s="4" t="s">
+      <c r="R43" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="K43" t="s">
-        <v>268</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="S43" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="T43" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="U43" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="M43" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="N43" s="11" t="s">
+      <c r="V43" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="O43" s="11" t="s">
+      <c r="W43" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="P43" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q43" s="11" t="s">
+      <c r="X43" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y43" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="R43" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="S43" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="T43" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="V43" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="W43" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="X43" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y43" s="11" t="s">
-        <v>280</v>
-      </c>
       <c r="Z43" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AA43" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AB43" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AC43" s="11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K44" t="s">
-        <v>237</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L44" t="s">
+        <v>232</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC44" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD44" s="3"/>
     </row>
     <row r="45" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K45" t="s">
-        <v>237</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L45" t="s">
+        <v>232</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC45" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD45" s="3"/>
     </row>
     <row r="46" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K46" t="s">
-        <v>237</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L46" t="s">
+        <v>232</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC46" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD46" s="3"/>
     </row>
     <row r="47" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K47" t="s">
-        <v>237</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L47" t="s">
+        <v>232</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC47" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD47" s="3"/>
     </row>
     <row r="48" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K48" t="s">
-        <v>237</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L48" t="s">
+        <v>232</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y48" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC48" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD48" s="3"/>
     </row>
     <row r="49" spans="1:30" s="11" customFormat="1" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K49" t="s">
-        <v>237</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V49" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y49" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA49" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC49" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B50" s="3">
         <v>10</v>
@@ -5694,13 +5716,13 @@
       <c r="J50" s="4">
         <v>6</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="4">
         <v>8</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L50">
         <v>10</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="1">
         <v>8</v>
       </c>
       <c r="N50" s="3">
@@ -5755,15 +5777,14 @@
     </row>
     <row r="51" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="J51" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="M51" s="3"/>
+        <v>384</v>
+      </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
@@ -5784,457 +5805,457 @@
     </row>
     <row r="52" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K52" t="s">
-        <v>240</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L52" t="s">
+        <v>235</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Y52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AC52" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AD52" s="3"/>
     </row>
     <row r="53" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K53" t="s">
-        <v>78</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L53" t="s">
+        <v>76</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Z53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AB53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AC53" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AD53" s="3"/>
     </row>
     <row r="54" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K54" t="s">
-        <v>240</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L54" t="s">
+        <v>235</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Y54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AC54" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AD54" s="3"/>
     </row>
     <row r="55" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K55" t="s">
-        <v>78</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L55" t="s">
+        <v>76</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Z55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AB55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AC55" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AD55" s="3"/>
     </row>
     <row r="56" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K56" t="s">
-        <v>78</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L56" t="s">
+        <v>76</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Z56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AB56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AC56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AD56" s="3"/>
     </row>
     <row r="57" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B57" s="3">
         <v>10</v>
@@ -6263,13 +6284,13 @@
       <c r="J57" s="4">
         <v>6</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="4">
         <v>8</v>
       </c>
-      <c r="L57" s="1">
+      <c r="L57">
         <v>10</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="1">
         <v>8</v>
       </c>
       <c r="N57" s="3">
@@ -6324,12 +6345,11 @@
     </row>
     <row r="58" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
-      <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
@@ -6353,7 +6373,6 @@
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
-      <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
@@ -6377,7 +6396,6 @@
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
-      <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
@@ -6407,9 +6425,9 @@
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-      <c r="K61"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="17"/>
+      <c r="K61" s="4"/>
+      <c r="L61"/>
+      <c r="M61" s="1"/>
       <c r="N61" s="17"/>
       <c r="O61" s="17"/>
       <c r="P61" s="17"/>
@@ -6430,187 +6448,187 @@
     </row>
     <row r="62" spans="1:30" ht="70.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K62" t="s">
-        <v>237</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L62" t="s">
+        <v>232</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC62" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD62" s="3"/>
     </row>
     <row r="63" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K63" t="s">
-        <v>237</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>237</v>
+        <v>76</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L63" t="s">
+        <v>232</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC63" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD63" s="3"/>
     </row>
     <row r="64" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B64" s="3">
         <v>10</v>
@@ -6639,13 +6657,13 @@
       <c r="J64" s="4">
         <v>6</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="4">
         <v>8</v>
       </c>
-      <c r="L64" s="1">
+      <c r="L64">
         <v>9</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M64" s="1">
         <v>7</v>
       </c>
       <c r="N64" s="3">
@@ -6700,12 +6718,11 @@
     </row>
     <row r="65" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
-      <c r="M65" s="3"/>
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
@@ -6729,7 +6746,6 @@
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
-      <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
@@ -6753,7 +6769,6 @@
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
-      <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
@@ -6774,367 +6789,367 @@
     </row>
     <row r="68" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K68" t="s">
-        <v>237</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L68" t="s">
+        <v>232</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC68" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD68" s="3"/>
     </row>
     <row r="69" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K69" t="s">
-        <v>237</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L69" t="s">
+        <v>232</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC69" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD69" s="3"/>
     </row>
     <row r="70" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="K70" t="s">
-        <v>240</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>240</v>
+        <v>380</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L70" t="s">
+        <v>235</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Y70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AC70" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AD70" s="3"/>
     </row>
     <row r="71" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="G71" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="H71" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="I71" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="J71" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="L71" t="s">
         <v>303</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="M71" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="N71" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="O71" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="I71" s="4" t="s">
+      <c r="P71" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="J71" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="K71" t="s">
-        <v>396</v>
-      </c>
-      <c r="L71" s="1" t="s">
+      <c r="Q71" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="R71" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="N71" s="3" t="s">
+      <c r="S71" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="O71" s="3" t="s">
+      <c r="T71" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="P71" s="3" t="s">
+      <c r="U71" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="Q71" s="3" t="s">
+      <c r="V71" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="R71" s="3" t="s">
+      <c r="W71" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="S71" s="3" t="s">
+      <c r="X71" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="T71" s="3" t="s">
+      <c r="Y71" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="U71" s="3" t="s">
+      <c r="Z71" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="V71" s="3" t="s">
+      <c r="AA71" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="W71" s="3" t="s">
+      <c r="AB71" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="X71" s="3" t="s">
+      <c r="AC71" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="Y71" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="Z71" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="AA71" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="AB71" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="AC71" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="AD71" s="3"/>
     </row>
     <row r="72" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B72" s="3">
         <v>10</v>
@@ -7163,13 +7178,13 @@
       <c r="J72" s="4">
         <v>7</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="4">
         <v>8</v>
       </c>
-      <c r="L72" s="1">
+      <c r="L72">
         <v>9</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="1">
         <v>7</v>
       </c>
       <c r="N72" s="3">
@@ -7224,12 +7239,11 @@
     </row>
     <row r="73" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
-      <c r="M73" s="3"/>
       <c r="N73" s="3"/>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
@@ -7253,7 +7267,6 @@
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
-      <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
@@ -7277,7 +7290,6 @@
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
-      <c r="M75" s="3"/>
       <c r="N75" s="3"/>
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
@@ -7307,9 +7319,9 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
-      <c r="K76"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="17"/>
+      <c r="K76" s="4"/>
+      <c r="L76"/>
+      <c r="M76" s="1"/>
       <c r="N76" s="17"/>
       <c r="O76" s="17"/>
       <c r="P76" s="17"/>
@@ -7330,13 +7342,12 @@
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
-      <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
@@ -7357,283 +7368,282 @@
     </row>
     <row r="78" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K78" t="s">
-        <v>237</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L78" t="s">
+        <v>232</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC78" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD78" s="4"/>
     </row>
     <row r="79" spans="1:30" ht="99" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="21" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K79" t="s">
-        <v>237</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L79" t="s">
+        <v>232</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC79" s="22" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD79" s="22"/>
     </row>
     <row r="80" spans="1:30" ht="84.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H80" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="I80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="L80" t="s">
+        <v>327</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="O80" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="P80" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="G80" s="4" t="s">
+      <c r="Q80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="R80" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="S80" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="K80" t="s">
+      <c r="T80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="U80" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="L80" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="M80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="N80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="O80" s="4" t="s">
+      <c r="V80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="W80" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="X80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="Z80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA80" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB80" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="AC80" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="P80" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="R80" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="S80" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="T80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="U80" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="V80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="W80" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="X80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="Y80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="Z80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA80" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB80" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="AC80" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="AD80" s="4"/>
     </row>
     <row r="81" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="21" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
       <c r="D81" s="22"/>
       <c r="E81" s="23"/>
-      <c r="M81" s="22"/>
       <c r="N81" s="22"/>
       <c r="O81" s="22"/>
       <c r="P81" s="22"/>
@@ -7654,13 +7664,12 @@
     </row>
     <row r="82" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="21" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
       <c r="D82" s="22"/>
       <c r="E82" s="23"/>
-      <c r="M82" s="22"/>
       <c r="N82" s="22"/>
       <c r="O82" s="22"/>
       <c r="P82" s="22"/>
@@ -7681,97 +7690,97 @@
     </row>
     <row r="83" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="K83" t="s">
-        <v>346</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="M83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="L83" t="s">
+        <v>341</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="Q83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="R83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="S83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="T83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="U83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="V83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="W83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="X83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="Y83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="Z83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AA83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AB83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AC83" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AD83" s="4"/>
     </row>
     <row r="84" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B84" s="3">
         <v>10</v>
@@ -7800,13 +7809,13 @@
       <c r="J84" s="4">
         <v>8</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="4">
         <v>8</v>
       </c>
-      <c r="L84" s="1">
-        <v>10</v>
-      </c>
-      <c r="M84" s="3">
+      <c r="L84">
+        <v>9</v>
+      </c>
+      <c r="M84" s="1">
         <v>8</v>
       </c>
       <c r="N84" s="3">
@@ -7861,12 +7870,11 @@
     </row>
     <row r="85" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
-      <c r="M85" s="3"/>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
@@ -7890,7 +7898,6 @@
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
-      <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
@@ -7920,9 +7927,9 @@
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
-      <c r="K87"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="17"/>
+      <c r="K87" s="4"/>
+      <c r="L87"/>
+      <c r="M87" s="1"/>
       <c r="N87" s="17"/>
       <c r="O87" s="17"/>
       <c r="P87" s="17"/>
@@ -7946,7 +7953,6 @@
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
-      <c r="M88" s="3"/>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
@@ -7967,13 +7973,12 @@
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
-      <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
       <c r="P89" s="4"/>
@@ -7994,97 +7999,97 @@
     </row>
     <row r="90" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K90" t="s">
-        <v>237</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L90" t="s">
+        <v>232</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC90" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD90" s="3"/>
     </row>
     <row r="91" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B91" s="3">
         <v>10</v>
@@ -8113,13 +8118,13 @@
       <c r="J91" s="4">
         <v>8</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="4">
         <v>8</v>
       </c>
-      <c r="L91" s="1">
-        <v>9</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="L91">
+        <v>8</v>
+      </c>
+      <c r="M91" s="1">
         <v>8</v>
       </c>
       <c r="N91" s="3">
@@ -8174,12 +8179,11 @@
     </row>
     <row r="92" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
-      <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
@@ -8203,7 +8207,6 @@
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
-      <c r="M93" s="3"/>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
@@ -8233,9 +8236,9 @@
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
-      <c r="K94"/>
-      <c r="L94" s="1"/>
-      <c r="M94" s="17"/>
+      <c r="K94" s="4"/>
+      <c r="L94"/>
+      <c r="M94" s="1"/>
       <c r="N94" s="17"/>
       <c r="O94" s="17"/>
       <c r="P94" s="17"/>
@@ -8259,7 +8262,6 @@
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
-      <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
@@ -8280,463 +8282,462 @@
     </row>
     <row r="96" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K96" t="s">
-        <v>237</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L96" t="s">
+        <v>232</v>
+      </c>
+      <c r="M96" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC96" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD96" s="3"/>
     </row>
     <row r="97" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="K97" t="s">
-        <v>240</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L97" t="s">
+        <v>232</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="T97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="W97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA97" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AB97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC97" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD97" s="3"/>
     </row>
     <row r="98" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K98" t="s">
-        <v>237</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L98" t="s">
+        <v>232</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC98" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD98" s="3"/>
     </row>
     <row r="99" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K99" t="s">
-        <v>237</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L99" t="s">
+        <v>232</v>
+      </c>
+      <c r="M99" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC99" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD99" s="3"/>
     </row>
     <row r="100" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K100" t="s">
-        <v>237</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L100" t="s">
+        <v>232</v>
+      </c>
+      <c r="M100" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC100" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD100" s="3"/>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A101" s="5" t="s">
-        <v>356</v>
+    <row r="101" spans="1:30" ht="28.3" x14ac:dyDescent="0.35">
+      <c r="A101" s="9" t="s">
+        <v>351</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="4"/>
-      <c r="M101" s="3"/>
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
@@ -8757,187 +8758,187 @@
     </row>
     <row r="102" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K102" t="s">
-        <v>237</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L102" t="s">
+        <v>232</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC102" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD102" s="3"/>
     </row>
     <row r="103" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K103" t="s">
-        <v>237</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L103" t="s">
+        <v>232</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC103" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD103" s="3"/>
     </row>
     <row r="104" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B104" s="3">
         <v>10</v>
@@ -8966,13 +8967,13 @@
       <c r="J104" s="4">
         <v>8</v>
       </c>
-      <c r="K104">
+      <c r="K104" s="4">
         <v>7</v>
       </c>
-      <c r="L104" s="1">
-        <v>10</v>
-      </c>
-      <c r="M104" s="3">
+      <c r="L104">
+        <v>8</v>
+      </c>
+      <c r="M104" s="1">
         <v>7</v>
       </c>
       <c r="N104" s="3">
@@ -9027,12 +9028,11 @@
     </row>
     <row r="105" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
-      <c r="M105" s="3"/>
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
@@ -9056,7 +9056,6 @@
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
-      <c r="M106" s="3"/>
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
@@ -9086,9 +9085,9 @@
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
-      <c r="K107"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="17"/>
+      <c r="K107" s="4"/>
+      <c r="L107"/>
+      <c r="M107" s="1"/>
       <c r="N107" s="17"/>
       <c r="O107" s="17"/>
       <c r="P107" s="17"/>
@@ -9112,7 +9111,6 @@
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
-      <c r="M108" s="3"/>
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
@@ -9133,367 +9131,367 @@
     </row>
     <row r="109" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K109" t="s">
-        <v>237</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L109" t="s">
+        <v>232</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC109" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD109" s="3"/>
     </row>
     <row r="110" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K110" t="s">
-        <v>237</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L110" t="s">
+        <v>232</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC110" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD110" s="3"/>
     </row>
     <row r="111" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K111" t="s">
-        <v>237</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L111" t="s">
+        <v>232</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Z111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC111" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD111" s="3"/>
     </row>
     <row r="112" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="K112" t="s">
-        <v>237</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="L112" t="s">
+        <v>232</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Q112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="T112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="U112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="V112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="W112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="X112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Z112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AA112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AB112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AC112" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AD112" s="3"/>
     </row>
     <row r="113" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B113" s="3">
         <v>10</v>
@@ -9522,13 +9520,13 @@
       <c r="J113" s="4">
         <v>8</v>
       </c>
-      <c r="K113">
+      <c r="K113" s="4">
         <v>7</v>
       </c>
-      <c r="L113" s="1">
-        <v>10</v>
-      </c>
-      <c r="M113" s="3">
+      <c r="L113">
+        <v>9</v>
+      </c>
+      <c r="M113" s="1">
         <v>7</v>
       </c>
       <c r="N113" s="3">
@@ -9583,12 +9581,11 @@
     </row>
     <row r="114" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
-      <c r="M114" s="3"/>
       <c r="N114" s="3"/>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
@@ -9612,7 +9609,6 @@
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
-      <c r="M115" s="3"/>
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
@@ -9642,9 +9638,9 @@
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
-      <c r="K116"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="17"/>
+      <c r="K116" s="4"/>
+      <c r="L116"/>
+      <c r="M116" s="1"/>
       <c r="N116" s="17"/>
       <c r="O116" s="17"/>
       <c r="P116" s="17"/>
@@ -9668,7 +9664,6 @@
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
-      <c r="M117" s="3"/>
       <c r="N117" s="3"/>
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
@@ -9689,13 +9684,12 @@
     </row>
     <row r="118" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="24" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
       <c r="D118" s="22"/>
       <c r="E118" s="23"/>
-      <c r="M118" s="22"/>
       <c r="N118" s="22"/>
       <c r="O118" s="22"/>
       <c r="P118" s="22"/>
@@ -9716,13 +9710,12 @@
     </row>
     <row r="119" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="24" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
       <c r="D119" s="22"/>
       <c r="E119" s="23"/>
-      <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="22"/>
       <c r="P119" s="22"/>
@@ -9743,13 +9736,12 @@
     </row>
     <row r="120" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="24" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
       <c r="D120" s="22"/>
       <c r="E120" s="23"/>
-      <c r="M120" s="22"/>
       <c r="N120" s="22"/>
       <c r="O120" s="22"/>
       <c r="P120" s="22"/>
@@ -9770,13 +9762,12 @@
     </row>
     <row r="121" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="24" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
       <c r="D121" s="22"/>
       <c r="E121" s="23"/>
-      <c r="M121" s="22"/>
       <c r="N121" s="22"/>
       <c r="O121" s="22"/>
       <c r="P121" s="22"/>
@@ -9797,13 +9788,12 @@
     </row>
     <row r="122" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="24" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B122" s="22"/>
       <c r="C122" s="22"/>
       <c r="D122" s="22"/>
       <c r="E122" s="23"/>
-      <c r="M122" s="22"/>
       <c r="N122" s="22"/>
       <c r="O122" s="22"/>
       <c r="P122" s="22"/>
@@ -9824,13 +9814,12 @@
     </row>
     <row r="123" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="24" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B123" s="22"/>
       <c r="C123" s="22"/>
       <c r="D123" s="22"/>
       <c r="E123" s="23"/>
-      <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="22"/>
       <c r="P123" s="22"/>
@@ -9851,13 +9840,12 @@
     </row>
     <row r="124" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="24" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
       <c r="D124" s="22"/>
       <c r="E124" s="23"/>
-      <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="22"/>
       <c r="P124" s="22"/>
@@ -9878,13 +9866,12 @@
     </row>
     <row r="125" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="24" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
       <c r="D125" s="22"/>
       <c r="E125" s="23"/>
-      <c r="M125" s="22"/>
       <c r="N125" s="22"/>
       <c r="O125" s="22"/>
       <c r="P125" s="22"/>
@@ -9905,13 +9892,12 @@
     </row>
     <row r="126" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="24" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
       <c r="D126" s="22"/>
       <c r="E126" s="23"/>
-      <c r="M126" s="22"/>
       <c r="N126" s="22"/>
       <c r="O126" s="22"/>
       <c r="P126" s="22"/>
@@ -9932,13 +9918,12 @@
     </row>
     <row r="127" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="24" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
       <c r="D127" s="22"/>
       <c r="E127" s="23"/>
-      <c r="M127" s="22"/>
       <c r="N127" s="22"/>
       <c r="O127" s="22"/>
       <c r="P127" s="22"/>
@@ -9959,13 +9944,12 @@
     </row>
     <row r="128" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="24" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B128" s="22"/>
       <c r="C128" s="22"/>
       <c r="D128" s="22"/>
       <c r="E128" s="23"/>
-      <c r="M128" s="22"/>
       <c r="N128" s="22"/>
       <c r="O128" s="22"/>
       <c r="P128" s="22"/>
@@ -9986,13 +9970,12 @@
     </row>
     <row r="129" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="24" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B129" s="22"/>
       <c r="C129" s="22"/>
       <c r="D129" s="22"/>
       <c r="E129" s="23"/>
-      <c r="M129" s="22"/>
       <c r="N129" s="22"/>
       <c r="O129" s="22"/>
       <c r="P129" s="22"/>
@@ -10013,13 +9996,12 @@
     </row>
     <row r="130" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="24" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B130" s="22"/>
       <c r="C130" s="22"/>
       <c r="D130" s="22"/>
       <c r="E130" s="23"/>
-      <c r="M130" s="22"/>
       <c r="N130" s="22"/>
       <c r="O130" s="22"/>
       <c r="P130" s="22"/>
@@ -10040,13 +10022,12 @@
     </row>
     <row r="131" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="24" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B131" s="22"/>
       <c r="C131" s="22"/>
       <c r="D131" s="22"/>
       <c r="E131" s="23"/>
-      <c r="M131" s="22"/>
       <c r="N131" s="22"/>
       <c r="O131" s="22"/>
       <c r="P131" s="22"/>
@@ -10067,13 +10048,12 @@
     </row>
     <row r="132" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="24" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B132" s="22"/>
       <c r="C132" s="22"/>
       <c r="D132" s="22"/>
       <c r="E132" s="23"/>
-      <c r="M132" s="22"/>
       <c r="N132" s="22"/>
       <c r="O132" s="22"/>
       <c r="P132" s="22"/>
@@ -10094,13 +10074,12 @@
     </row>
     <row r="133" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="24" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B133" s="22"/>
       <c r="C133" s="22"/>
       <c r="D133" s="22"/>
       <c r="E133" s="23"/>
-      <c r="M133" s="22"/>
       <c r="N133" s="22"/>
       <c r="O133" s="22"/>
       <c r="P133" s="22"/>
@@ -10121,13 +10100,12 @@
     </row>
     <row r="134" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="24" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B134" s="22"/>
       <c r="C134" s="22"/>
       <c r="D134" s="22"/>
       <c r="E134" s="23"/>
-      <c r="M134" s="22"/>
       <c r="N134" s="22"/>
       <c r="O134" s="22"/>
       <c r="P134" s="22"/>
@@ -10148,13 +10126,12 @@
     </row>
     <row r="135" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="24" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B135" s="22"/>
       <c r="C135" s="22"/>
       <c r="D135" s="22"/>
       <c r="E135" s="23"/>
-      <c r="M135" s="22"/>
       <c r="N135" s="22"/>
       <c r="O135" s="22"/>
       <c r="P135" s="22"/>
@@ -10187,6 +10164,10 @@
     <hyperlink ref="E16" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="I16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
     <hyperlink ref="K3" r:id="rId11" xr:uid="{99C752FD-9135-4ABC-ABCF-C75B7C7098E2}"/>
+    <hyperlink ref="L3" r:id="rId12" xr:uid="{380795D2-D41F-43DD-8E24-49C549A17FC0}"/>
+    <hyperlink ref="L16" r:id="rId13" xr:uid="{7F2D18CE-C043-440D-8832-0A2A05CCB8DE}"/>
+    <hyperlink ref="M3" r:id="rId14" xr:uid="{892021BB-F3F4-43DF-AD0F-717D95486219}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{BE69EA0C-93AA-44F2-AD9F-C6BA1FCE3D59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
+++ b/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\coding\AIMSS\StateOfPractice\DomainMeasurements\InverseKinematics-Ryan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC80BCA-11BB-4FD2-8948-913900E36316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C5BCBC-144C-403C-9661-51CFCF486BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="appendix-B-wide-summary" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="675">
   <si>
     <t>Metric
 指标（见附录 A 与附录 B）</t>
@@ -1425,84 +1425,6 @@
     <t>Doxygen,automated testing</t>
   </si>
   <si>
-    <t>Is there evidence of continuous integration? (for example mentioned in documentation, Jenkins, Travis CI, Bamboo, other) (yes∗, no, unclear)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/bazel.yml, .github/workflows/ci.yml, .github/workflows/docker-nightly.yml, .github/workflows/package_xml.yml, .github/workflows/pr-collection-labeler.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/sync_protected_branches.yml, .github/workflows/test_suite_linux.yml, .github/workflows/test_suite_linux_develop.yml, .github/workflows/test_suite_mac.yml, .github/workflows/test_suite_mac_develop.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/cmake.yml, appveyor.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/build.yml, .github/workflows/build_steps.sh, .github/workflows/lint.yml, .github/workflows/live.yml, .github/workflows/publish-wasm.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/mirror-rolling-to-master.yaml, .github/workflows/pr.yaml, .github/workflows/release-nightlies.yaml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/ci.yaml, .travis.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/clang_format.yml, .github/workflows/test_docs.yml, .github/workflows/test_macos.yml, .github/workflows/test_ubuntu.yml, .github/workflows/test_windows.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/stale.yml, .jenkins/Jenkinsfile-experimental, .jenkins/Jenkinsfile-external-examples, .jenkins/Jenkinsfile-production, .jenkins/Jenkinsfile-staging)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/cancel_branch_jobs.yml, .github/workflows/ci_altlinux.yml, .github/workflows/ci_freebsd.yml, .github/workflows/ci_gz_physics.yml, .github/workflows/ci_lint.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/_ci-ubuntu.yml, .github/workflows/ue4_content.yml, .github/workflows/ue4_dev.yml, .github/workflows/ue4_release.yml, .github/workflows/ue5_dev.yml)</t>
-  </si>
-  <si>
-    <t>yes (.travis.yml, appveyor.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/continuous_integration.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/before_all.sh, .github/workflows/before_build.sh, .github/workflows/before_build_windows.ps1, .github/workflows/build.yml, .github/workflows/format.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/check-changelog.yml, .github/workflows/check_label.yml, .github/workflows/cmake/linux-debug-toolchain.cmake, .github/workflows/dockgen.yml, .github/workflows/linux.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/main.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/build-and-test.yml, .github/workflows/ci-macos-linux-windows-pixi.yml, .github/workflows/launch-conda-packages-build.yml, .github/workflows/launch-perf-test.yml, .github/workflows/nightly-generate-binaries.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/ci.yaml, .github/workflows/docker.yaml, .github/workflows/docker_lint.yaml, .github/workflows/format.yaml, .github/workflows/prerelease.yaml)</t>
-  </si>
-  <si>
-    <t>yes (.travis.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/install_and_test.yml)</t>
-  </si>
-  <si>
-    <t>yes (appveyor.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/clang_format.yml, .github/workflows/cpp_unittests.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/build-linux.yml, .github/workflows/build-macos.yml, .github/workflows/build-windows.yml, .github/workflows/check-clang-format.yml, appveyor.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/build.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/ci.yml, .github/workflows/docker-build.yml, .github/workflows/nightly-merge.yml, .github/workflows/pr-commands.yml, .github/workflows/python.yml)</t>
-  </si>
-  <si>
-    <t>yes (.github/workflows/openrtm_linux.yml, azure-pipelines.yml)</t>
-  </si>
-  <si>
     <t>gz-sim10_10.0.0</t>
   </si>
   <si>
@@ -2033,168 +1955,9 @@
     <t>Numbers of commits by year in the last 5 years. (Count from as early as possible if the project is younger than 5 years.) (list of numbers)</t>
   </si>
   <si>
-    <t>2022: 475; 2023: 321; 2024: 290; 2025: 250; 2026: 81</t>
-  </si>
-  <si>
-    <t>2022: 1027; 2023: 608; 2024: 221; 2025: 53; 2026: 16</t>
-  </si>
-  <si>
-    <t>2022: 152; 2023: 8; 2024: 6; 2025: 5; 2026: 0</t>
-  </si>
-  <si>
-    <t>2022: 158; 2023: 251; 2024: 163; 2025: 166; 2026: 165</t>
-  </si>
-  <si>
-    <t>2022: 491; 2023: 840; 2024: 1244; 2025: 1315; 2026: 781</t>
-  </si>
-  <si>
-    <t>2022: 6; 2023: 9; 2024: 8; 2025: 10; 2026: 5</t>
-  </si>
-  <si>
-    <t>2022: 12; 2023: 9; 2024: 13; 2025: 31; 2026: 14</t>
-  </si>
-  <si>
-    <t>2022: 683; 2023: 889; 2024: 383; 2025: 0; 2026: 0</t>
-  </si>
-  <si>
-    <t>2022: 6; 2023: 8; 2024: 9; 2025: 14; 2026: 3</t>
-  </si>
-  <si>
-    <t>2022: 238; 2023: 0; 2024: 0; 2025: 1; 2026: 1</t>
-  </si>
-  <si>
-    <t>2022: 1713; 2023: 1618; 2024: 1247; 2025: 1251; 2026: 481</t>
-  </si>
-  <si>
-    <t>2022: 43; 2023: 7; 2024: 291; 2025: 394; 2026: 257</t>
-  </si>
-  <si>
-    <t>2022: 385; 2023: 269; 2024: 471; 2025: 113; 2026: 35</t>
-  </si>
-  <si>
-    <t>2022: 1; 2023: 0; 2024: 0; 2025: 0; 2026: 0</t>
-  </si>
-  <si>
-    <t>2022: 48; 2023: 13; 2024: 45; 2025: 25; 2026: 6</t>
-  </si>
-  <si>
-    <t>2022: 30; 2023: 68; 2024: 23; 2025: 298; 2026: 200</t>
-  </si>
-  <si>
-    <t>2022: 898; 2023: 556; 2024: 1743; 2025: 2343; 2026: 843</t>
-  </si>
-  <si>
-    <t>2022: 48; 2023: 14; 2024: 12; 2025: 22; 2026: 2</t>
-  </si>
-  <si>
-    <t>2022: 840; 2023: 409; 2024: 389; 2025: 338; 2026: 188</t>
-  </si>
-  <si>
-    <t>2022: 476; 2023: 331; 2024: 193; 2025: 117; 2026: 5</t>
-  </si>
-  <si>
-    <t>2022: 0; 2023: 0; 2024: 0; 2025: 0; 2026: 0</t>
-  </si>
-  <si>
-    <t>2022: 225; 2023: 162; 2024: 99; 2025: 19; 2026: 25</t>
-  </si>
-  <si>
-    <t>2022: 1216; 2023: 1294; 2024: 1386; 2025: 1236; 2026: 604</t>
-  </si>
-  <si>
-    <t>2022: 0; 2023: 1; 2024: 0; 2025: 0; 2026: 0</t>
-  </si>
-  <si>
-    <t>2022: 514; 2023: 437; 2024: 346; 2025: 130; 2026: 299</t>
-  </si>
-  <si>
-    <t>2022: 1774; 2023: 1441; 2024: 1193; 2025: 2722; 2026: 1141</t>
-  </si>
-  <si>
-    <t>2022: 336; 2023: 508; 2024: 262; 2025: 442; 2026: 82</t>
-  </si>
-  <si>
-    <t>2022: 221; 2023: 59; 2024: 69; 2025: 72; 2026: 40</t>
-  </si>
-  <si>
     <t>Numbers of commits by month in the last 12 months. (list of numbers)</t>
   </si>
   <si>
-    <t>2025-06: 15; 2025-07: 24; 2025-08: 40; 2025-09: 17; 2025-10: 16; 2025-11: 21; 2025-12: 11; 2026-01: 17; 2026-02: 27; 2026-03: 19; 2026-04: 9; 2026-05: 9</t>
-  </si>
-  <si>
-    <t>2025-06: 4; 2025-07: 9; 2025-08: 10; 2025-09: 0; 2025-10: 0; 2025-11: 2; 2025-12: 0; 2026-01: 0; 2026-02: 9; 2026-03: 3; 2026-04: 3; 2026-05: 1</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 0; 2025-08: 0; 2025-09: 0; 2025-10: 1; 2025-11: 0; 2025-12: 0; 2026-01: 0; 2026-02: 0; 2026-03: 0; 2026-04: 0; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 21; 2025-07: 19; 2025-08: 1; 2025-09: 8; 2025-10: 12; 2025-11: 39; 2025-12: 16; 2026-01: 8; 2026-02: 32; 2026-03: 43; 2026-04: 66; 2026-05: 16</t>
-  </si>
-  <si>
-    <t>2025-06: 74; 2025-07: 138; 2025-08: 111; 2025-09: 88; 2025-10: 140; 2025-11: 176; 2025-12: 115; 2026-01: 144; 2026-02: 203; 2026-03: 183; 2026-04: 177; 2026-05: 74</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 0; 2025-08: 0; 2025-09: 0; 2025-10: 0; 2025-11: 0; 2025-12: 0; 2026-01: 1; 2026-02: 0; 2026-03: 3; 2026-04: 1; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 3; 2025-07: 2; 2025-08: 0; 2025-09: 2; 2025-10: 7; 2025-11: 1; 2025-12: 4; 2026-01: 2; 2026-02: 1; 2026-03: 2; 2026-04: 9; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 0; 2025-08: 0; 2025-09: 0; 2025-10: 0; 2025-11: 0; 2025-12: 0; 2026-01: 0; 2026-02: 0; 2026-03: 0; 2026-04: 0; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 1; 2025-08: 0; 2025-09: 1; 2025-10: 2; 2025-11: 0; 2025-12: 0; 2026-01: 0; 2026-02: 0; 2026-03: 2; 2026-04: 1; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 0; 2025-08: 0; 2025-09: 0; 2025-10: 0; 2025-11: 0; 2025-12: 0; 2026-01: 0; 2026-02: 0; 2026-03: 1; 2026-04: 0; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 82; 2025-07: 84; 2025-08: 80; 2025-09: 131; 2025-10: 162; 2025-11: 79; 2025-12: 79; 2026-01: 76; 2026-02: 102; 2026-03: 119; 2026-04: 150; 2026-05: 34</t>
-  </si>
-  <si>
-    <t>2025-06: 4; 2025-07: 8; 2025-08: 22; 2025-09: 4; 2025-10: 44; 2025-11: 199; 2025-12: 63; 2026-01: 140; 2026-02: 19; 2026-03: 4; 2026-04: 5; 2026-05: 89</t>
-  </si>
-  <si>
-    <t>2025-06: 7; 2025-07: 1; 2025-08: 16; 2025-09: 5; 2025-10: 18; 2025-11: 18; 2025-12: 2; 2026-01: 3; 2026-02: 2; 2026-03: 6; 2026-04: 20; 2026-05: 4</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 3; 2025-08: 5; 2025-09: 0; 2025-10: 2; 2025-11: 1; 2025-12: 0; 2026-01: 2; 2026-02: 3; 2026-03: 1; 2026-04: 0; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 28; 2025-07: 0; 2025-08: 54; 2025-09: 3; 2025-10: 12; 2025-11: 0; 2025-12: 124; 2026-01: 41; 2026-02: 22; 2026-03: 83; 2026-04: 47; 2026-05: 7</t>
-  </si>
-  <si>
-    <t>2025-06: 90; 2025-07: 141; 2025-08: 49; 2025-09: 87; 2025-10: 108; 2025-11: 167; 2025-12: 302; 2026-01: 155; 2026-02: 280; 2026-03: 248; 2026-04: 154; 2026-05: 6</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 1; 2025-08: 3; 2025-09: 1; 2025-10: 6; 2025-11: 1; 2025-12: 6; 2026-01: 0; 2026-02: 1; 2026-03: 0; 2026-04: 0; 2026-05: 1</t>
-  </si>
-  <si>
-    <t>2025-06: 24; 2025-07: 30; 2025-08: 10; 2025-09: 25; 2025-10: 25; 2025-11: 25; 2025-12: 33; 2026-01: 34; 2026-02: 45; 2026-03: 83; 2026-04: 19; 2026-05: 7</t>
-  </si>
-  <si>
-    <t>2025-06: 9; 2025-07: 2; 2025-08: 1; 2025-09: 1; 2025-10: 5; 2025-11: 18; 2025-12: 14; 2026-01: 1; 2026-02: 0; 2026-03: 4; 2026-04: 0; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 0; 2025-08: 0; 2025-09: 0; 2025-10: 0; 2025-11: 0; 2025-12: 0; 2026-01: 3; 2026-02: 20; 2026-03: 0; 2026-04: 0; 2026-05: 2</t>
-  </si>
-  <si>
-    <t>2025-06: 52; 2025-07: 72; 2025-08: 93; 2025-09: 140; 2025-10: 155; 2025-11: 103; 2025-12: 103; 2026-01: 139; 2026-02: 134; 2026-03: 178; 2026-04: 104; 2026-05: 49</t>
-  </si>
-  <si>
-    <t>2025-06: 0; 2025-07: 1; 2025-08: 10; 2025-09: 5; 2025-10: 9; 2025-11: 21; 2025-12: 26; 2026-01: 73; 2026-02: 81; 2026-03: 100; 2026-04: 39; 2026-05: 6</t>
-  </si>
-  <si>
-    <t>2025-06: 339; 2025-07: 273; 2025-08: 204; 2025-09: 380; 2025-10: 284; 2025-11: 290; 2025-12: 242; 2026-01: 221; 2026-02: 199; 2026-03: 350; 2026-04: 300; 2026-05: 71</t>
-  </si>
-  <si>
-    <t>2025-06: 27; 2025-07: 57; 2025-08: 57; 2025-09: 27; 2025-10: 14; 2025-11: 33; 2025-12: 20; 2026-01: 36; 2026-02: 25; 2026-03: 13; 2026-04: 8; 2026-05: 0</t>
-  </si>
-  <si>
-    <t>2025-06: 4; 2025-07: 6; 2025-08: 0; 2025-09: 18; 2025-10: 10; 2025-11: 7; 2025-12: 6; 2026-01: 0; 2026-02: 0; 2026-03: 26; 2026-04: 9; 2026-05: 5</t>
-  </si>
-  <si>
     <t>Number of code lines in text-based files. (number)</t>
   </si>
   <si>
@@ -2217,13 +1980,225 @@
   </si>
   <si>
     <t>Number of closed pull requests. (number)</t>
+  </si>
+  <si>
+    <t>[475, 321, 290, 250, 81]</t>
+  </si>
+  <si>
+    <t>[1027, 608, 221, 53, 16]</t>
+  </si>
+  <si>
+    <t>[152, 8, 6, 5, 0]</t>
+  </si>
+  <si>
+    <t>[158, 251, 163, 166, 165]</t>
+  </si>
+  <si>
+    <t>[491, 840, 1244, 1315, 781]</t>
+  </si>
+  <si>
+    <t>[6, 9, 8, 10, 5]</t>
+  </si>
+  <si>
+    <t>[12, 9, 13, 31, 14]</t>
+  </si>
+  <si>
+    <t>[683, 889, 383, 0, 0]</t>
+  </si>
+  <si>
+    <t>[6, 8, 9, 14, 3]</t>
+  </si>
+  <si>
+    <t>[238, 0, 0, 1, 1]</t>
+  </si>
+  <si>
+    <t>[1713, 1618, 1247, 1251, 481]</t>
+  </si>
+  <si>
+    <t>[43, 7, 291, 394, 257]</t>
+  </si>
+  <si>
+    <t>[385, 269, 471, 113, 35]</t>
+  </si>
+  <si>
+    <t>[1, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[48, 13, 45, 25, 6]</t>
+  </si>
+  <si>
+    <t>[30, 68, 23, 298, 201]</t>
+  </si>
+  <si>
+    <t>[898, 556, 1743, 2343, 843]</t>
+  </si>
+  <si>
+    <t>[48, 14, 12, 22, 2]</t>
+  </si>
+  <si>
+    <t>[840, 409, 389, 338, 188]</t>
+  </si>
+  <si>
+    <t>[476, 331, 193, 117, 5]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[225, 162, 99, 19, 25]</t>
+  </si>
+  <si>
+    <t>[1216, 1294, 1386, 1236, 604]</t>
+  </si>
+  <si>
+    <t>[0, 1, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[514, 437, 346, 130, 299]</t>
+  </si>
+  <si>
+    <t>[1774, 1441, 1193, 2722, 1142]</t>
+  </si>
+  <si>
+    <t>[336, 508, 262, 442, 82]</t>
+  </si>
+  <si>
+    <t>[221, 59, 69, 72, 40]</t>
+  </si>
+  <si>
+    <t>[15, 24, 40, 17, 16, 21, 11, 17, 27, 19, 9, 9]</t>
+  </si>
+  <si>
+    <t>[4, 9, 10, 0, 0, 2, 0, 0, 9, 3, 3, 1]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[21, 19, 1, 8, 12, 39, 16, 8, 32, 43, 66, 16]</t>
+  </si>
+  <si>
+    <t>[74, 138, 111, 88, 140, 176, 115, 144, 203, 183, 177, 74]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0, 0, 0, 1, 0, 3, 1, 0]</t>
+  </si>
+  <si>
+    <t>[3, 2, 0, 2, 7, 1, 4, 2, 1, 2, 9, 0]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[0, 1, 0, 1, 2, 0, 0, 0, 0, 2, 1, 0]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0]</t>
+  </si>
+  <si>
+    <t>[82, 84, 80, 131, 162, 79, 79, 76, 102, 119, 150, 34]</t>
+  </si>
+  <si>
+    <t>[4, 8, 22, 4, 44, 199, 63, 140, 19, 4, 5, 89]</t>
+  </si>
+  <si>
+    <t>[7, 1, 16, 5, 18, 18, 2, 3, 2, 6, 20, 4]</t>
+  </si>
+  <si>
+    <t>[0, 3, 5, 0, 2, 1, 0, 2, 3, 1, 0, 0]</t>
+  </si>
+  <si>
+    <t>[28, 0, 54, 3, 12, 0, 124, 41, 22, 83, 47, 8]</t>
+  </si>
+  <si>
+    <t>[90, 141, 49, 87, 108, 167, 302, 155, 280, 248, 154, 6]</t>
+  </si>
+  <si>
+    <t>[0, 1, 3, 1, 6, 1, 6, 0, 1, 0, 0, 1]</t>
+  </si>
+  <si>
+    <t>[24, 30, 10, 25, 25, 25, 33, 34, 45, 83, 19, 7]</t>
+  </si>
+  <si>
+    <t>[9, 2, 1, 1, 5, 18, 14, 1, 0, 4, 0, 0]</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0, 0, 0, 0, 3, 20, 0, 0, 2]</t>
+  </si>
+  <si>
+    <t>[52, 72, 93, 140, 155, 103, 103, 139, 134, 178, 104, 49]</t>
+  </si>
+  <si>
+    <t>[0, 1, 10, 5, 9, 21, 26, 73, 81, 100, 39, 6]</t>
+  </si>
+  <si>
+    <t>[339, 273, 204, 380, 284, 290, 242, 221, 199, 350, 300, 72]</t>
+  </si>
+  <si>
+    <t>[27, 57, 57, 27, 14, 33, 20, 36, 25, 13, 8, 0]</t>
+  </si>
+  <si>
+    <t>[4, 6, 0, 18, 10, 7, 6, 0, 0, 26, 9, 5]</t>
+  </si>
+  <si>
+    <t>yes (performance-related code or documentation references)</t>
+  </si>
+  <si>
+    <t>yes (ANN library includes performance counting macros)</t>
+  </si>
+  <si>
+    <t>yes (blast/include/extensions/authoring/NvBlastExtAuthoringFractureTool.h, blast/include/extensions/stress/NvBlastExtStressSolver.h)</t>
+  </si>
+  <si>
+    <t>yes (DART_BUILD_PROFILE, DART_PROFILE_TRACY, DART_ENABLE_SIMD options, compiler cache)</t>
+  </si>
+  <si>
+    <t>yes (performance-focused changes documented in changelog)</t>
+  </si>
+  <si>
+    <t>yes (VAMP integration with SIMD, build type options for Release/RelWithDebInfo, parallel builds)</t>
+  </si>
+  <si>
+    <t>yes (benchmark infrastructure, tracy profiler option, CRTP pattern mentioned)</t>
+  </si>
+  <si>
+    <t>yes (parallel execution options, performance optimizations mentioned)</t>
+  </si>
+  <si>
+    <t>yes (SSE/AVX/GPU solver options, parallel processing, caching)</t>
+  </si>
+  <si>
+    <r>
+      <t>Is there evidence that performance was considered? Performance refers to either speed, storage, or throughput. (yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>∗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, no)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2279,6 +2254,20 @@
       <sz val="11"/>
       <name val="Cambria Math"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4096,7 +4085,7 @@
         <v>167</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>168</v>
@@ -6533,93 +6522,93 @@
       </c>
       <c r="AD48" s="3"/>
     </row>
-    <row r="49" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="U49" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="V49" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="W49" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="X49" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="Z49" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="AA49" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="AB49" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="AC49" s="1" t="s">
-        <v>452</v>
+    <row r="49" spans="1:30" customFormat="1" ht="86.15" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>674</v>
+      </c>
+      <c r="B49" t="s">
+        <v>665</v>
+      </c>
+      <c r="C49" t="s">
+        <v>665</v>
+      </c>
+      <c r="D49" t="s">
+        <v>665</v>
+      </c>
+      <c r="E49" t="s">
+        <v>665</v>
+      </c>
+      <c r="F49" t="s">
+        <v>665</v>
+      </c>
+      <c r="G49" t="s">
+        <v>665</v>
+      </c>
+      <c r="H49" t="s">
+        <v>665</v>
+      </c>
+      <c r="I49" t="s">
+        <v>666</v>
+      </c>
+      <c r="J49" t="s">
+        <v>667</v>
+      </c>
+      <c r="K49" t="s">
+        <v>665</v>
+      </c>
+      <c r="L49" t="s">
+        <v>665</v>
+      </c>
+      <c r="M49" t="s">
+        <v>668</v>
+      </c>
+      <c r="N49" t="s">
+        <v>669</v>
+      </c>
+      <c r="O49" t="s">
+        <v>665</v>
+      </c>
+      <c r="P49" t="s">
+        <v>665</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>670</v>
+      </c>
+      <c r="R49" t="s">
+        <v>671</v>
+      </c>
+      <c r="S49" t="s">
+        <v>665</v>
+      </c>
+      <c r="T49" t="s">
+        <v>672</v>
+      </c>
+      <c r="U49" t="s">
+        <v>665</v>
+      </c>
+      <c r="V49" t="s">
+        <v>665</v>
+      </c>
+      <c r="W49" t="s">
+        <v>665</v>
+      </c>
+      <c r="X49" t="s">
+        <v>665</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>665</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>665</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>673</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>665</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
@@ -8279,91 +8268,91 @@
     </row>
     <row r="77" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A77" s="17" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>131</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="J77" s="17" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="L77" s="17" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="M77" s="17" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="N77" s="17" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="O77" s="17" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="P77" s="17" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="Q77" s="17" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="R77" s="17" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="S77" s="17" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="T77" s="17" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="U77" s="17" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="V77" s="17" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="W77" s="17" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="X77" s="17" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="Y77" s="17" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="Z77" s="17" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="AA77" s="17" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="AB77" s="17" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="AC77" s="17" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
     </row>
     <row r="78" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
@@ -8458,91 +8447,91 @@
     </row>
     <row r="79" spans="1:30" s="17" customFormat="1" ht="70.75" x14ac:dyDescent="0.35">
       <c r="A79" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="E79" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="G79" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="J79" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="K79" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="L79" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="M79" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="O79" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="P79" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q79" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="R79" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="S79" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="T79" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="U79" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="V79" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="W79" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="X79" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="Y79" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="Z79" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="AA79" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="AB79" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="AC79" s="17" t="s">
         <v>484</v>
-      </c>
-      <c r="D79" s="17" t="s">
-        <v>485</v>
-      </c>
-      <c r="E79" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="G79" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="H79" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="I79" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="J79" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="K79" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="L79" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="M79" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="N79" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="O79" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="P79" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q79" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="R79" s="17" t="s">
-        <v>499</v>
-      </c>
-      <c r="S79" s="17" t="s">
-        <v>500</v>
-      </c>
-      <c r="T79" s="17" t="s">
-        <v>501</v>
-      </c>
-      <c r="U79" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="V79" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="W79" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="X79" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="Y79" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="Z79" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="AA79" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="AB79" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="AC79" s="17" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="80" spans="1:30" ht="84.9" customHeight="1" x14ac:dyDescent="0.35">
@@ -8637,180 +8626,180 @@
     </row>
     <row r="81" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A81" s="17" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="G81" s="17" t="s">
         <v>76</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="J81" s="17" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="K81" s="17" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="L81" s="17" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="M81" s="17" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="N81" s="17" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="O81" s="17" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="P81" s="17" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="Q81" s="17" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="R81" s="17" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="S81" s="17" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="T81" s="17" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="U81" s="17" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="V81" s="17" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="W81" s="17" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="X81" s="17" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="Y81" s="17" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="Z81" s="17" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="AA81" s="17" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="AB81" s="17" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="AC81" s="17" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
     </row>
     <row r="82" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="E82" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="F82" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="G82" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="J82" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="K82" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="L82" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="M82" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="O82" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="P82" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q82" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="R82" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="S82" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="T82" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="U82" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="V82" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="W82" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="X82" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="Y82" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="Z82" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="AA82" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="AB82" s="17" t="s">
         <v>539</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="AC82" s="17" t="s">
         <v>540</v>
-      </c>
-      <c r="D82" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="E82" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="G82" s="17" t="s">
-        <v>544</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="I82" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="J82" s="17" t="s">
-        <v>547</v>
-      </c>
-      <c r="K82" s="17" t="s">
-        <v>548</v>
-      </c>
-      <c r="L82" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="M82" s="17" t="s">
-        <v>550</v>
-      </c>
-      <c r="N82" s="17" t="s">
-        <v>551</v>
-      </c>
-      <c r="O82" s="17" t="s">
-        <v>552</v>
-      </c>
-      <c r="P82" s="17" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q82" s="17" t="s">
-        <v>554</v>
-      </c>
-      <c r="R82" s="17" t="s">
-        <v>555</v>
-      </c>
-      <c r="S82" s="17" t="s">
-        <v>556</v>
-      </c>
-      <c r="T82" s="17" t="s">
-        <v>557</v>
-      </c>
-      <c r="U82" s="17" t="s">
-        <v>558</v>
-      </c>
-      <c r="V82" s="17" t="s">
-        <v>559</v>
-      </c>
-      <c r="W82" s="17" t="s">
-        <v>560</v>
-      </c>
-      <c r="X82" s="17" t="s">
-        <v>561</v>
-      </c>
-      <c r="Y82" s="17" t="s">
-        <v>562</v>
-      </c>
-      <c r="Z82" s="17" t="s">
-        <v>563</v>
-      </c>
-      <c r="AA82" s="17" t="s">
-        <v>564</v>
-      </c>
-      <c r="AB82" s="17" t="s">
-        <v>565</v>
-      </c>
-      <c r="AC82" s="17" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="83" spans="1:30" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -9098,91 +9087,91 @@
     </row>
     <row r="89" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="E89" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="G89" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="H89" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="I89" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="J89" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="K89" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="L89" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="M89" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="N89" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="O89" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="P89" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q89" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="R89" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="S89" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="T89" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="U89" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="V89" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="W89" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="X89" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="Y89" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="Z89" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="AA89" s="17" t="s">
         <v>567</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="AB89" s="17" t="s">
         <v>568</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="AC89" s="17" t="s">
         <v>569</v>
-      </c>
-      <c r="D89" s="17" t="s">
-        <v>570</v>
-      </c>
-      <c r="E89" s="17" t="s">
-        <v>571</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>572</v>
-      </c>
-      <c r="G89" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="H89" s="17" t="s">
-        <v>574</v>
-      </c>
-      <c r="I89" s="17" t="s">
-        <v>575</v>
-      </c>
-      <c r="J89" s="17" t="s">
-        <v>576</v>
-      </c>
-      <c r="K89" s="17" t="s">
-        <v>577</v>
-      </c>
-      <c r="L89" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="M89" s="17" t="s">
-        <v>579</v>
-      </c>
-      <c r="N89" s="17" t="s">
-        <v>580</v>
-      </c>
-      <c r="O89" s="17" t="s">
-        <v>581</v>
-      </c>
-      <c r="P89" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="Q89" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="R89" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="S89" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="T89" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="U89" s="17" t="s">
-        <v>587</v>
-      </c>
-      <c r="V89" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="W89" s="17" t="s">
-        <v>589</v>
-      </c>
-      <c r="X89" s="17" t="s">
-        <v>590</v>
-      </c>
-      <c r="Y89" s="17" t="s">
-        <v>591</v>
-      </c>
-      <c r="Z89" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="AA89" s="17" t="s">
-        <v>593</v>
-      </c>
-      <c r="AB89" s="17" t="s">
-        <v>594</v>
-      </c>
-      <c r="AC89" s="17" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="90" spans="1:30" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
@@ -10319,91 +10308,91 @@
     </row>
     <row r="109" spans="1:30" s="17" customFormat="1" ht="28.3" x14ac:dyDescent="0.35">
       <c r="A109" s="17" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>599</v>
+        <v>573</v>
       </c>
       <c r="E109" s="17" t="s">
         <v>131</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="G109" s="17" t="s">
         <v>131</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="J109" s="17" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
       <c r="L109" s="17" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="M109" s="17" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>607</v>
+        <v>581</v>
       </c>
       <c r="O109" s="17" t="s">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="P109" s="17" t="s">
-        <v>609</v>
+        <v>583</v>
       </c>
       <c r="Q109" s="17" t="s">
         <v>131</v>
       </c>
       <c r="R109" s="17" t="s">
-        <v>610</v>
+        <v>584</v>
       </c>
       <c r="S109" s="17" t="s">
-        <v>611</v>
+        <v>585</v>
       </c>
       <c r="T109" s="17" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
       <c r="U109" s="17" t="s">
-        <v>613</v>
+        <v>587</v>
       </c>
       <c r="V109" s="17" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="W109" s="17" t="s">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="X109" s="17" t="s">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="Y109" s="17" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>618</v>
+        <v>592</v>
       </c>
       <c r="AA109" s="17" t="s">
-        <v>619</v>
+        <v>593</v>
       </c>
       <c r="AB109" s="17" t="s">
-        <v>620</v>
+        <v>594</v>
       </c>
       <c r="AC109" s="17" t="s">
-        <v>621</v>
+        <v>595</v>
       </c>
     </row>
     <row r="110" spans="1:30" ht="42.45" customHeight="1" x14ac:dyDescent="0.35">
@@ -10906,7 +10895,7 @@
     </row>
     <row r="119" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="B119">
         <v>1765</v>
@@ -11000,7 +10989,7 @@
     </row>
     <row r="120" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="B120">
         <v>210</v>
@@ -11094,7 +11083,7 @@
     </row>
     <row r="121" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="B121">
         <v>704551</v>
@@ -11188,7 +11177,7 @@
     </row>
     <row r="122" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="B122">
         <v>1460745</v>
@@ -11282,7 +11271,7 @@
     </row>
     <row r="123" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="B123">
         <v>691522</v>
@@ -11376,7 +11365,7 @@
     </row>
     <row r="124" spans="1:34" ht="56.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="B124">
         <v>7500</v>
@@ -11468,197 +11457,187 @@
       <c r="AG124"/>
       <c r="AH124"/>
     </row>
-    <row r="125" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:34" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>602</v>
+      </c>
+      <c r="B125" t="s">
+        <v>612</v>
+      </c>
+      <c r="C125" t="s">
+        <v>613</v>
+      </c>
+      <c r="D125" t="s">
+        <v>614</v>
+      </c>
+      <c r="E125" t="s">
+        <v>615</v>
+      </c>
+      <c r="F125" t="s">
+        <v>616</v>
+      </c>
+      <c r="G125" t="s">
+        <v>617</v>
+      </c>
+      <c r="H125" t="s">
+        <v>618</v>
+      </c>
+      <c r="I125" t="s">
+        <v>619</v>
+      </c>
+      <c r="J125" t="s">
+        <v>620</v>
+      </c>
+      <c r="K125" t="s">
+        <v>621</v>
+      </c>
+      <c r="L125" t="s">
+        <v>622</v>
+      </c>
+      <c r="M125" t="s">
+        <v>623</v>
+      </c>
+      <c r="N125" t="s">
+        <v>624</v>
+      </c>
+      <c r="O125" t="s">
+        <v>625</v>
+      </c>
+      <c r="P125" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>627</v>
+      </c>
+      <c r="R125" t="s">
         <v>628</v>
       </c>
-      <c r="B125" t="s">
+      <c r="S125" t="s">
         <v>629</v>
       </c>
-      <c r="C125" t="s">
+      <c r="T125" t="s">
         <v>630</v>
       </c>
-      <c r="D125" t="s">
+      <c r="U125" t="s">
         <v>631</v>
       </c>
-      <c r="E125" t="s">
+      <c r="V125" t="s">
         <v>632</v>
       </c>
-      <c r="F125" t="s">
+      <c r="W125" t="s">
         <v>633</v>
       </c>
-      <c r="G125" t="s">
+      <c r="X125" t="s">
         <v>634</v>
       </c>
-      <c r="H125" t="s">
+      <c r="Y125" t="s">
         <v>635</v>
       </c>
-      <c r="I125" t="s">
+      <c r="Z125" t="s">
         <v>636</v>
       </c>
-      <c r="J125" t="s">
+      <c r="AA125" t="s">
         <v>637</v>
       </c>
-      <c r="K125" t="s">
+      <c r="AB125" t="s">
         <v>638</v>
       </c>
-      <c r="L125" t="s">
+      <c r="AC125" t="s">
         <v>639</v>
       </c>
-      <c r="M125" t="s">
+    </row>
+    <row r="126" spans="1:34" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>603</v>
+      </c>
+      <c r="B126" t="s">
         <v>640</v>
       </c>
-      <c r="N125" t="s">
+      <c r="C126" t="s">
         <v>641</v>
       </c>
-      <c r="O125" t="s">
+      <c r="D126" t="s">
         <v>642</v>
       </c>
-      <c r="P125" t="s">
+      <c r="E126" t="s">
         <v>643</v>
       </c>
-      <c r="Q125" t="s">
+      <c r="F126" t="s">
         <v>644</v>
       </c>
-      <c r="R125" t="s">
+      <c r="G126" t="s">
         <v>645</v>
       </c>
-      <c r="S125" t="s">
+      <c r="H126" t="s">
         <v>646</v>
       </c>
-      <c r="T125" t="s">
+      <c r="I126" t="s">
         <v>647</v>
       </c>
-      <c r="U125" t="s">
+      <c r="J126" t="s">
         <v>648</v>
       </c>
-      <c r="V125" t="s">
+      <c r="K126" t="s">
         <v>649</v>
       </c>
-      <c r="W125" t="s">
+      <c r="L126" t="s">
         <v>650</v>
       </c>
-      <c r="X125" t="s">
+      <c r="M126" t="s">
         <v>651</v>
       </c>
-      <c r="Y125" t="s">
+      <c r="N126" t="s">
         <v>652</v>
       </c>
-      <c r="Z125" t="s">
+      <c r="O126" t="s">
+        <v>647</v>
+      </c>
+      <c r="P126" t="s">
         <v>653</v>
       </c>
-      <c r="AA125" t="s">
+      <c r="Q126" t="s">
         <v>654</v>
       </c>
-      <c r="AB125" t="s">
+      <c r="R126" t="s">
         <v>655</v>
       </c>
-      <c r="AC125" t="s">
+      <c r="S126" t="s">
         <v>656</v>
       </c>
-      <c r="AD125"/>
-      <c r="AE125"/>
-      <c r="AF125"/>
-      <c r="AG125"/>
-      <c r="AH125"/>
-    </row>
-    <row r="126" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="T126" t="s">
         <v>657</v>
       </c>
-      <c r="B126" t="s">
+      <c r="U126" t="s">
         <v>658</v>
       </c>
-      <c r="C126" t="s">
+      <c r="V126" t="s">
+        <v>647</v>
+      </c>
+      <c r="W126" t="s">
         <v>659</v>
       </c>
-      <c r="D126" t="s">
+      <c r="X126" t="s">
         <v>660</v>
       </c>
-      <c r="E126" t="s">
+      <c r="Y126" t="s">
+        <v>647</v>
+      </c>
+      <c r="Z126" t="s">
         <v>661</v>
       </c>
-      <c r="F126" t="s">
+      <c r="AA126" t="s">
         <v>662</v>
       </c>
-      <c r="G126" t="s">
+      <c r="AB126" t="s">
         <v>663</v>
       </c>
-      <c r="H126" t="s">
+      <c r="AC126" t="s">
         <v>664</v>
       </c>
-      <c r="I126" t="s">
-        <v>665</v>
-      </c>
-      <c r="J126" t="s">
-        <v>666</v>
-      </c>
-      <c r="K126" t="s">
-        <v>667</v>
-      </c>
-      <c r="L126" t="s">
-        <v>668</v>
-      </c>
-      <c r="M126" t="s">
-        <v>669</v>
-      </c>
-      <c r="N126" t="s">
-        <v>670</v>
-      </c>
-      <c r="O126" t="s">
-        <v>665</v>
-      </c>
-      <c r="P126" t="s">
-        <v>671</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>672</v>
-      </c>
-      <c r="R126" t="s">
-        <v>673</v>
-      </c>
-      <c r="S126" t="s">
-        <v>674</v>
-      </c>
-      <c r="T126" t="s">
-        <v>675</v>
-      </c>
-      <c r="U126" t="s">
-        <v>676</v>
-      </c>
-      <c r="V126" t="s">
-        <v>665</v>
-      </c>
-      <c r="W126" t="s">
-        <v>677</v>
-      </c>
-      <c r="X126" t="s">
-        <v>678</v>
-      </c>
-      <c r="Y126" t="s">
-        <v>665</v>
-      </c>
-      <c r="Z126" t="s">
-        <v>679</v>
-      </c>
-      <c r="AA126" t="s">
-        <v>680</v>
-      </c>
-      <c r="AB126" t="s">
-        <v>681</v>
-      </c>
-      <c r="AC126" t="s">
-        <v>682</v>
-      </c>
-      <c r="AD126"/>
-      <c r="AE126"/>
-      <c r="AF126"/>
-      <c r="AG126"/>
-      <c r="AH126"/>
     </row>
     <row r="127" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="B127">
         <v>1765</v>
@@ -11752,7 +11731,7 @@
     </row>
     <row r="128" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="B128">
         <v>704551</v>
@@ -11846,7 +11825,7 @@
     </row>
     <row r="129" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>683</v>
+        <v>604</v>
       </c>
       <c r="B129">
         <v>193808</v>
@@ -11940,7 +11919,7 @@
     </row>
     <row r="130" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>684</v>
+        <v>605</v>
       </c>
       <c r="B130">
         <v>83838</v>
@@ -12034,7 +12013,7 @@
     </row>
     <row r="131" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>685</v>
+        <v>606</v>
       </c>
       <c r="B131">
         <v>77856</v>
@@ -12128,7 +12107,7 @@
     </row>
     <row r="132" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>686</v>
+        <v>607</v>
       </c>
       <c r="B132">
         <v>1337</v>
@@ -12222,7 +12201,7 @@
     </row>
     <row r="133" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>687</v>
+        <v>608</v>
       </c>
       <c r="B133">
         <v>411</v>
@@ -12316,7 +12295,7 @@
     </row>
     <row r="134" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>688</v>
+        <v>609</v>
       </c>
       <c r="B134">
         <v>22</v>
@@ -12410,7 +12389,7 @@
     </row>
     <row r="135" spans="1:34" ht="28.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
       <c r="B135">
         <v>92</v>
@@ -12504,7 +12483,7 @@
     </row>
     <row r="136" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>690</v>
+        <v>611</v>
       </c>
       <c r="B136">
         <v>2358</v>

--- a/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
+++ b/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/summary.xlsx
@@ -22,8 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="690">
   <si>
-    <t>Metric
-指标（见附录 A 与附录 B）</t>
+    <t>Metric</t>
   </si>
   <si>
     <t>Gazebo</t>
@@ -146,8 +145,7 @@
     <t>YARP (Yet Another Robot Platform)</t>
   </si>
   <si>
-    <t>URL? (URL)
-网址（URL）</t>
+    <t>URL? (URL)</t>
   </si>
   <si>
     <t>https://gazebosim.org</t>
@@ -189,8 +187,7 @@
     <t>https://www.openrtm.org</t>
   </si>
   <si>
-    <t>Affiliation (institution(s)) (string or N/A)
-所属机构（字符串或 N/A）</t>
+    <t>Affiliation (institution(s)) (string or N/A)</t>
   </si>
   <si>
     <t>Open Source Robotics Foundation (OSRF)</t>
@@ -277,8 +274,7 @@
     <t>National Institute of Advanced Industrial Science and Technology (AIST), Japan; primary developer: Noriaki Ando (AIST Intelligent Systems Research Institute); OpenRTM-aist Project team at AIST</t>
   </si>
   <si>
-    <t>Software purpose (string)
-软件用途（字符串）</t>
+    <t>Software purpose (string)</t>
   </si>
   <si>
     <t>Open-source robotics simulator providing high-fidelity physics, rendering, and sensor models for robot simulation and testing</t>
@@ -365,8 +361,7 @@
     <t>Robotic Technology Middleware (RTM) implementation for the OMG-standardized RT (Robot Technology) Component standard; provides a component-based framework for creating, managing and connecting RT-Components (robot software modules); enables distributed robot systems by abstracting hardware and software interfaces into standardized components; includes component framework, execution context management, CORBA-based inter-component communication, and development tools (RTCBuilder, RTSystemEditor); widely used in Japanese robotics industry and research</t>
   </si>
   <si>
-    <t>How is the project funded? (unfunded, unclear, funded∗) where ∗ requires a string to say the source of funding
-项目如何获得资金支持？（无资助、不明确、有资助∗；若有资助需写明来源）</t>
+    <t>How is the project funded? (unfunded, unclear, funded∗) where ∗ requires a string to say the source of funding</t>
   </si>
   <si>
     <t>funded (Open Source Robotics Foundation through contracts, grants, and donations from DARPA, NASA, Amazon, Bosch, Nvidia, Toyota Research Institute, and others)</t>
@@ -390,8 +385,7 @@
     <t>dead</t>
   </si>
   <si>
-    <t>License? (GNU GPL, BSD, MIT, terms of use, trial, none, unclear, other∗) ∗ given via a string
-许可证？（GNU GPL、BSD、MIT、使用条款、试用版、无、不明确、其他∗；∗需写明具体内容）</t>
+    <t>License? (GNU GPL, BSD, MIT, terms of use, trial, none, unclear, other∗) ∗ given via a string</t>
   </si>
   <si>
     <t>other (Apache-2.0)</t>
@@ -427,8 +421,7 @@
     <t>other (LGPL-2.1)</t>
   </si>
   <si>
-    <t>Platforms? (set of Windows, Linux, OS X, Android, other∗) ∗ given via string
-支持的平台？（Windows、Linux、OS X、Android、其他∗ 的集合；∗需写明）</t>
+    <t>Platforms? (set of Windows, Linux, OS X, Android, other∗) ∗ given via string</t>
   </si>
   <si>
     <t>Windows, Linux, OS X</t>
@@ -449,26 +442,22 @@
     <t>Windows, Linux, OS X, Android</t>
   </si>
   <si>
-    <t>Software Category? The concept category includes software that does not have an officially released version. Public software has a released version in the public domain. Private software has a released version available to authorized users only. (concept, public, private)
-软件类别？若尚无正式发布版本则为概念版；已公开发布为公开软件；仅授权用户可用为私有软件。（概念、公开、私有）</t>
+    <t>Software Category? The concept category includes software that does not have an officially released version. Public software has a released version in the public domain. Private software has a released version available to authorized users only. (concept, public, private)</t>
   </si>
   <si>
     <t>public</t>
   </si>
   <si>
-    <t>Development model? (open source, freeware, commercial, unclear)
-开发模式？（开源、免费软件、商业软件、不明确）</t>
+    <t>Development model? (open source, freeware, commercial, unclear)</t>
   </si>
   <si>
     <t>commercial</t>
   </si>
   <si>
-    <t>Publications about the software? Refers to publications that have used or mentioned the software. (number or unknown)
-关于该软件的论文数量？指使用或提及该软件的出版物。（数字或 unknown）</t>
-  </si>
-  <si>
-    <t>Source code URL? (set of url, n/a, unclear)
-源代码网址？（URL 集合、n/a 或 unclear）</t>
+    <t>Publications about the software? Refers to publications that have used or mentioned the software. (number or unknown)</t>
+  </si>
+  <si>
+    <t>Source code URL? (set of url, n/a, unclear)</t>
   </si>
   <si>
     <t>https://github.com/gazebosim/gz-sim</t>
@@ -540,8 +529,7 @@
     <t>https://github.com/OpenRTM/OpenRTM-aist</t>
   </si>
   <si>
-    <t>Is there evidence that performance was considered? Performance refers to either speed, storage, or throughput. (yes∗, no)
-是否有证据表明考虑过性能？性能指速度、存储或吞吐量。（是∗、否）</t>
+    <t>Is there evidence that performance was considered? Performance refers to either speed, storage, or throughput. (yes∗, no)</t>
   </si>
   <si>
     <t xml:space="preserve">yes </t>
@@ -550,43 +538,34 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Additional comments? (can cover any metrics you feel are missing
-补充说明？（可填写遗漏指标或任何其他想法）</t>
-  </si>
-  <si>
-    <t>Are there installation instructions? (yes,no)
-是否有安装说明？（是、否）</t>
+    <t>Additional comments? (can cover any metrics you feel are missing</t>
+  </si>
+  <si>
+    <t>Are there installation instructions? (yes,no)</t>
   </si>
   <si>
     <t>no</t>
   </si>
   <si>
-    <t>Are the installation instructions linear? Linear meaning progressing in a single series of steps. (yes, no, n/a)
-安装说明是否为线性步骤？即按单一路径依次执行。（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Are the instructions written as if the person doing the installation has none of the dependent packages installed? (yes, no, unclear)
-说明是否假设安装者尚未安装任何依赖包？（是、否、不明确）</t>
-  </si>
-  <si>
-    <t>Are compatible operating system versions listed? (yes, no)
-是否列出了兼容的操作系统版本？（是、否）</t>
-  </si>
-  <si>
-    <t>Is there something in place to automate the installation (makefile, script, installer, etc)? (yes∗, no)
-是否有自动化安装方式（如 makefile、脚本、安装器等）？（是∗、否）</t>
-  </si>
-  <si>
-    <t>If the software installation broke, was a descriptive error message displayed? (yes, no, n/a)
-如果安装失败，是否显示了有描述性的错误信息？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Is there a specified way to validate the installation? (yes∗, no)
-是否指定了验证安装是否成功的方法？（是∗、否）</t>
-  </si>
-  <si>
-    <t>How many steps were involved in the installation? (Includes manual steps like unzipping files) Specify OS. (number, OS)
-安装一共涉及多少步骤？（包含解压等人工步骤；请注明操作系统）（数字，OS）</t>
+    <t>Are the installation instructions linear? Linear meaning progressing in a single series of steps. (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Are the instructions written as if the person doing the installation has none of the dependent packages installed? (yes, no, unclear)</t>
+  </si>
+  <si>
+    <t>Are compatible operating system versions listed? (yes, no)</t>
+  </si>
+  <si>
+    <t>Is there something in place to automate the installation (makefile, script, installer, etc)? (yes∗, no)</t>
+  </si>
+  <si>
+    <t>If the software installation broke, was a descriptive error message displayed? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Is there a specified way to validate the installation? (yes∗, no)</t>
+  </si>
+  <si>
+    <t>How many steps were involved in the installation? (Includes manual steps like unzipping files) Specify OS. (number, OS)</t>
   </si>
   <si>
     <t>2,Linux</t>
@@ -607,78 +586,61 @@
     <t>4, Linux</t>
   </si>
   <si>
-    <t>What OS was used for the installation? (Windows, Linux, OS X, Android, other∗ ) ∗given via string
-安装使用的操作系统是什么？（Windows、Linux、OS X、Android、其他∗；∗需写明）</t>
-  </si>
-  <si>
-    <t>How many extra software packages need to be installed before or during installation? (number)
-安装前或安装过程中需要额外安装多少软件包？（数字）</t>
-  </si>
-  <si>
-    <t>Are required package versions listed? (yes, no, n/a)
-是否列出了所需软件包的版本？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Are there instructions for the installation of required packages / dependencies? (yes, no, n/a)
-是否提供了所需软件包/依赖项的安装说明？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Overall impression? (1 .. 10)
-总体印象？（1 到 10）</t>
+    <t>What OS was used for the installation? (Windows, Linux, OS X, Android, other∗ ) ∗given via string</t>
+  </si>
+  <si>
+    <t>How many extra software packages need to be installed before or during installation? (number)</t>
+  </si>
+  <si>
+    <t>Are required package versions listed? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Are there instructions for the installation of required packages / dependencies? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Overall impression? (1 .. 10)</t>
   </si>
   <si>
     <t>the document doesn't write very well, it is hard for beginner.The official installation instructions appear outdated. The guide is from 2006 and uses old build steps such as GNU make, VC6 project files, manual copying of library/header files, and MacOS X X11 setup.</t>
   </si>
   <si>
-    <t>Are the tutorial instructions linear? (yes, no, n/a)
-教程说明是否是线性的？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Does the getting started tutorial provide an expected output? (yes, no*, n/a)
-入门教程是否提供了预期输出？（是、否*、n/a）</t>
-  </si>
-  <si>
-    <t>Does your tutorial output match the expected output? (yes, no, n/a)
-你的教程输出是否与预期输出一致？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Are unit tests available? (yes, no, unclear)
-是否提供单元测试？（是、否、不明确）</t>
-  </si>
-  <si>
-    <t>Did the software "break" during installation? (yes∗ , no)
-软件在安装过程中是否“崩掉”过？（是∗、否）</t>
-  </si>
-  <si>
-    <t>Did the software "break" during the initial tutorial testing? (yes∗, no, n/a)
-软件在初始教程测试中是否“崩掉”过？（是∗、否、n/a）</t>
-  </si>
-  <si>
-    <t>If the tutorial testing broke, was a descriptive error message displayed? (yes, no, n/a)
-若教程测试崩掉，是否显示了有描述性的错误信息？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>If the tutorial testing broke, was the tutorial testing instance recoverable? (yes, no, n/a)
-若教程测试崩掉，教程测试实例是否可恢复？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Does the software handle unexpected/unanticipated input (like data of the wrong type, empty input, missing files or links) reasonably? (a reasonable response can include an appropriate error message.) (yes, no∗ )
-软件是否能合理处理意外/非预期输入（如错误类型数据、空输入、缺失文件或链接）？合理响应可包括合适的错误信息。（是、否∗）</t>
-  </si>
-  <si>
-    <t>For any plain text input files, if all new lines are replaced with new lines and carriage returns, will the software handle this gracefully? (yes, no∗, n/a)
-对于纯文本输入文件，如果把所有换行替换成回车换行，软件是否仍能正常处理？（是、否∗、n/a）</t>
+    <t>Are the tutorial instructions linear? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Does the getting started tutorial provide an expected output? (yes, no*, n/a)</t>
+  </si>
+  <si>
+    <t>Does your tutorial output match the expected output? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Are unit tests available? (yes, no, unclear)</t>
+  </si>
+  <si>
+    <t>Did the software "break" during installation? (yes∗ , no)</t>
+  </si>
+  <si>
+    <t>Did the software "break" during the initial tutorial testing? (yes∗, no, n/a)</t>
+  </si>
+  <si>
+    <t>If the tutorial testing broke, was a descriptive error message displayed? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>If the tutorial testing broke, was the tutorial testing instance recoverable? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Does the software handle unexpected/unanticipated input (like data of the wrong type, empty input, missing files or links) reasonably? (a reasonable response can include an appropriate error message.) (yes, no∗ )</t>
+  </si>
+  <si>
+    <t>For any plain text input files, if all new lines are replaced with new lines and carriage returns, will the software handle this gracefully? (yes, no∗, n/a)</t>
   </si>
   <si>
     <t>To be measured</t>
   </si>
   <si>
-    <t>Is there a user manual? (yes, no)
-是否有用户手册？（是、否）</t>
-  </si>
-  <si>
-    <t>What is the user support model? FAQ? User forum? E-mail address to direct questions? Etc. (string)
-用户支持模式是什么？FAQ、用户论坛、答疑邮箱等。（字符串）</t>
+    <t>Is there a user manual? (yes, no)</t>
+  </si>
+  <si>
+    <t>What is the user support model? FAQ? User forum? E-mail address to direct questions? Etc. (string)</t>
   </si>
   <si>
     <t>Community forum (community.gazebosim.org), GitHub Issues, comprehensive documentation site (gazebosim.org/docs), ROS Answers integration</t>
@@ -756,15 +718,13 @@
     <t>openrtm.org forum (Japanese and English), GitHub Issues (OpenRTM/OpenRTM-aist), AIST mailing list for commercial inquiries</t>
   </si>
   <si>
-    <t>Is there any information on how code is reviewed, or how to contribute? (yes∗, no)
-是否有关于代码评审或如何贡献代码的信息？（是∗、否）</t>
+    <t>Is there any information on how code is reviewed, or how to contribute? (yes∗, no)</t>
   </si>
   <si>
     <t>yes (GitHub pull request workflow, contribution guidelines, code of conduct documented)</t>
   </si>
   <si>
-    <t>What issue tracking tool is employed? (set of Trac, JIRA, Redmine, e-mail, discussion board, sourceforge, google code, git, BitBucket, none, unclear, other∗) ∗ given via string
-使用了什么问题跟踪工具？（Trac、JIRA、Redmine、电子邮件、讨论板、SourceForge、Google Code、git、BitBucket、无、不明确、其他∗ 的集合；∗需写明）</t>
+    <t>What issue tracking tool is employed? (set of Trac, JIRA, Redmine, e-mail, discussion board, sourceforge, google code, git, BitBucket, none, unclear, other∗) ∗ given via string</t>
   </si>
   <si>
     <t>git</t>
@@ -803,8 +763,7 @@
     <t>git (GitHub Issues; previously SourceForge and AIST Trac)</t>
   </si>
   <si>
-    <t>Which version control system is in use? (svn, cvs, git, Github, unclear, other∗) ∗ given via string
-使用的是哪种版本控制系统？（svn、cvs、git、Github、不明确、其他∗；∗需写明）</t>
+    <t>Which version control system is in use? (svn, cvs, git, Github, unclear, other∗) ∗ given via string</t>
   </si>
   <si>
     <t>Github</t>
@@ -813,58 +772,46 @@
     <t>other and github</t>
   </si>
   <si>
-    <t>Is API documented? (yes, no, n/a)
-API 是否有文档？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Consistent indentation and formatting style? (yes, no, n/a)
-缩进和格式风格是否一致？（是、否、n/a）</t>
-  </si>
-  <si>
-    <t>Explicit identification of a coding standard? (yes∗, no, n/a)
-是否明确标识了编码规范？（是∗、否、n/a）</t>
-  </si>
-  <si>
-    <t>Are the code identifiers consistent, distinctive, and meaningful? (yes, no∗ , n/a)
-代码标识符是否一致、易区分且有意义？（是、否∗、n/a）</t>
-  </si>
-  <si>
-    <t>Are constants (other than 0 and 1) hard coded into the program? (yes, no∗ , n/a)
-除 0 和 1 外，常量是否被硬编码到程序中？（是、否∗、n/a）</t>
+    <t>Is API documented? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Consistent indentation and formatting style? (yes, no, n/a)</t>
+  </si>
+  <si>
+    <t>Explicit identification of a coding standard? (yes∗, no, n/a)</t>
+  </si>
+  <si>
+    <t>Are the code identifiers consistent, distinctive, and meaningful? (yes, no∗ , n/a)</t>
+  </si>
+  <si>
+    <t>Are constants (other than 0 and 1) hard coded into the program? (yes, no∗ , n/a)</t>
   </si>
   <si>
     <t>yes (some magic constants appear in sampled source files)</t>
   </si>
   <si>
-    <t>Comments are clear, indicate what is being done, not how? (yes, no∗ , n/a)
-注释是否清晰，说明做了什么而不是怎么做？（是、否∗、n/a）</t>
-  </si>
-  <si>
-    <t>Parameters are in the same order for all functions? (yes, no∗ , n/a)
-所有函数的参数顺序是否一致？（是、否∗、n/a）</t>
-  </si>
-  <si>
-    <t>Is the name/URL of any algorithms used mentioned? (yes, no∗ , n/a)
-是否提到了所用算法的名称/URL？（是、否∗、n/a）</t>
-  </si>
-  <si>
-    <t>Is code modularized? (yes, no∗ , n/a)
-代码是否模块化？（是、否∗、n/a）</t>
-  </si>
-  <si>
-    <t>Are there any documents recording the development process and status? (yes∗, no))
-是否有记录开发过程和状态的文档？（是∗、否）</t>
+    <t>Comments are clear, indicate what is being done, not how? (yes, no∗ , n/a)</t>
+  </si>
+  <si>
+    <t>Parameters are in the same order for all functions? (yes, no∗ , n/a)</t>
+  </si>
+  <si>
+    <t>Is the name/URL of any algorithms used mentioned? (yes, no∗ , n/a)</t>
+  </si>
+  <si>
+    <t>Is code modularized? (yes, no∗ , n/a)</t>
+  </si>
+  <si>
+    <t>Are there any documents recording the development process and status? (yes∗, no))</t>
   </si>
   <si>
     <t>yes (GitHub Issues, pull requests, release notes)</t>
   </si>
   <si>
-    <t>Is the development environment documented? (yes∗, no)
-是否记录了开发环境？（是∗、否）</t>
-  </si>
-  <si>
-    <t>Are there release notes? (yes∗, no)
-是否有发布说明？（是∗、否）</t>
+    <t>Is the development environment documented? (yes∗, no)</t>
+  </si>
+  <si>
+    <t>Are there release notes? (yes∗, no)</t>
   </si>
   <si>
     <t>Windows</t>
@@ -907,8 +854,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Are the installation instructions in one place? Place referring to a single document or web-page. (yes, no, n/a)
-安装说明是否集中在一个地方？即单一文档或网页。（是、否、n/a）</t>
+    <t>Are the installation instructions in one place? Place referring to a single document or web-page. (yes, no, n/a)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2072,8 +2018,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Are expected user characteristics documented? (yes, no)
-是否记录了预期用户特征？（是、否）</t>
+    <t>Are expected user characteristics documented? (yes, no)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2101,13 +2046,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>If there is a getting started tutorial? (yes, no)
-是否有入门教程？（是、否）</t>
+    <t>If there is a getting started tutorial? (yes, no)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Is there a getting started tutorial? (yes, no)
-是否有入门教程？（是、否）</t>
+    <t>Is there a getting started tutorial? (yes, no)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2115,8 +2058,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Software name? (string)
-软件名称（字符串）</t>
+    <t>Software name? (string)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2130,8 +2072,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>If the software installation broke, was the installation instance recoverable? (yes, no, n/a)
-若安装过程崩掉，安装实例是否可恢复？（是、否、n/a）</t>
+    <t>If the software installation broke, was the installation instance recoverable? (yes, no, n/a)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2177,8 +2118,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Status? (alive is defined as presence of commits in the last 18 months) (alive, dead, unclear)
-项目状态？（若过去 18 个月内有提交则视为存活；选项为存活、停止维护、不明确）</t>
+    <t>Status? (alive is defined as presence of commits in the last 18 months) (alive, dead, unclear)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2206,14 +2146,12 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> , no, unclear)
-是否有对程序需求规格说明或理论手册的引用？</t>
+      <t xml:space="preserve"> , no, unclear)</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Overall impression? (1 .. 10)
-总体印象？（1 到 10）</t>
+    <t>Overall impression? (1 .. 10)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2258,8 +2196,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> , no, unavail)
-如果有卸载功能，执行卸载后是否造成明显问题？（是、否、不可用）</t>
+      <t xml:space="preserve"> , no, unavail)</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
